--- a/GameConfig/Datas/_import_v1_preview/叙事Session配置表.xlsx
+++ b/GameConfig/Datas/_import_v1_preview/叙事Session配置表.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="叙事Session配置表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="叙事Session配置表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,6 +426,8 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -484,6 +486,16 @@
           <t>backgroundId</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>titleDate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>titleLocation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -541,6 +553,16 @@
           <t>string</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -598,6 +620,16 @@
           <t>c</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -653,6 +685,16 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>场景背景 ID；为空时回退到按 npcId 选择（旧逻辑）</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>开场过场卡日期，如 2026年9月30日；为空则本幕不播过场</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>开场过场卡地点，如 老周修理铺；为空则本幕不播过场</t>
         </is>
       </c>
     </row>
@@ -707,6 +749,16 @@
           <t>scene_shop_old</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026年9月30日</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>老周修理铺</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -759,6 +811,16 @@
           <t>scene_zhou</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026年10月6日</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>仓库</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -802,6 +864,16 @@
       <c r="K7" t="inlineStr">
         <is>
           <t>scene_chenguo</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026年10月10日</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>陈果房间</t>
         </is>
       </c>
     </row>
@@ -858,6 +930,8 @@
           <t>scene_shop_old</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -912,6 +986,16 @@
           <t>scene_father</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026年10月15日</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>父母房间</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -964,6 +1048,16 @@
       <c r="K10" t="inlineStr">
         <is>
           <t>scene_shop_old</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026年10月16日</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>老周修理铺</t>
         </is>
       </c>
     </row>
@@ -1021,6 +1115,16 @@
           <t>scene_shop_new</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026年10月22日</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>老周修理铺</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -1072,6 +1176,16 @@
           <t>scene_father</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026年10月27日</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>父母房间</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -1111,6 +1225,16 @@
       <c r="K13" t="inlineStr">
         <is>
           <t>scene_shop_new</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026年10月30日</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>老周修理铺</t>
         </is>
       </c>
     </row>
